--- a/tables_and_figures/table5_jaccard_categories.xlsx
+++ b/tables_and_figures/table5_jaccard_categories.xlsx
@@ -430,7 +430,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4231221159792588</v>
+        <v>0.4231221159792589</v>
       </c>
     </row>
     <row r="3">
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5896825396825396</v>
+        <v>0.5896825396825397</v>
       </c>
     </row>
     <row r="4">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5952380952380951</v>
+        <v>0.5952380952380952</v>
       </c>
     </row>
   </sheetData>
